--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-FRM-23_dis_laboratuvar__kalibrasyon_saglayicisi_kapsam_ve_yete.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/04_Laboratuvar, COP ve Test Kapsamı/EKG-KLT-FRM-23_dis_laboratuvar__kalibrasyon_saglayicisi_kapsam_ve_yete.xlsx
@@ -987,7 +987,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-23&amp;C&amp;"Arial,Regular"&amp;11Dış Laboratuvar / Kalibrasyon Sağlayıcısı Kapsam ve Yeterlilik Değerlendirme…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Sağlayıcı yeterliliği kapsamı müşteri, kalite sistemi ve mevzuat şartlarına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54f7178374af42a4"/>
   <x:tableParts count="1">
@@ -1323,7 +1324,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-23&amp;C&amp;"Arial,Regular"&amp;11Dış Laboratuvar / Kalibrasyon Sağlayıcısı Kapsam ve Yeterlilik Değerlendirme…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Sağlayıcı yeterliliği kapsamı müşteri, kalite sistemi ve mevzuat şartlarına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a51e3d6f6844166"/>
   <x:tableParts count="1">
@@ -1636,7 +1638,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-23&amp;C&amp;"Arial,Regular"&amp;11Dış Laboratuvar / Kalibrasyon Sağlayıcısı Kapsam ve Yeterlilik Değerlendirme…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Sağlayıcı yeterliliği kapsamı müşteri, kalite sistemi ve mevzuat şartlarına bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5de740dba59c4d4d"/>
   <x:tableParts count="1">
